--- a/jogos_2026-04-05.xlsx
+++ b/jogos_2026-04-05.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1443,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.03</v>
+        <v>4.51</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.42</v>
+        <v>3.96</v>
       </c>
       <c r="R76" t="n">
-        <v>3.54</v>
+        <v>1.69</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>6.17</v>
+        <v>1.47</v>
       </c>
       <c r="Q77" t="n">
         <v>4.99</v>
       </c>
       <c r="R77" t="n">
-        <v>1.47</v>
+        <v>6.17</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>4.51</v>
+        <v>6.17</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.96</v>
+        <v>4.99</v>
       </c>
       <c r="R78" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,16 +15818,16 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.99</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>6.17</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16021,10 +16021,10 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19949,10 +19949,10 @@
         <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20737,10 +20737,10 @@
         <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28820,10 +28820,10 @@
         <v>0</v>
       </c>
       <c r="AE144" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF144" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG144" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,10 +30002,10 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF150" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>2.01</v>
+        <v>6.79</v>
       </c>
       <c r="Q151" t="n">
-        <v>4.06</v>
+        <v>4.85</v>
       </c>
       <c r="R151" t="n">
-        <v>3.68</v>
+        <v>1.4</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,16 +30199,16 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF151" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG151" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH151" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>6.79</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30402,10 +30402,10 @@
         <v>0</v>
       </c>
       <c r="AG152" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH152" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI152" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30993,10 +30993,10 @@
         <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH155" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>6.24</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31387,10 +31387,10 @@
         <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH157" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31529,137 +31529,137 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P158" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R158" t="n">
-        <v>2.25</v>
+        <v>2.78</v>
       </c>
       <c r="S158" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U158" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V158" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W158" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X158" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z158" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AF158" t="n">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="AG158" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH158" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI158" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ158" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK158" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL158" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM158" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN158" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO158" t="n">
         <v>0</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR158" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS158" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT158" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU158" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV158" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AW158" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX158" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY158" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ158" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BA158" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BB158" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC158" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD158" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE158" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF158" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG158" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q159" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31775,10 +31775,10 @@
         <v>0</v>
       </c>
       <c r="AE159" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF159" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31923,137 +31923,137 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S160" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T160" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U160" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V160" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W160" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X160" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y160" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z160" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA160" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB160" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC160" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD160" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE160" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF160" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG160" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH160" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI160" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ160" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK160" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL160" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM160" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN160" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO160" t="n">
         <v>0</v>
       </c>
       <c r="AP160" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR160" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS160" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU160" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV160" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW160" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX160" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY160" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ160" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA160" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BB160" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC160" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD160" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE160" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF160" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG160" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q165" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q185" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="Q193" t="n">
-        <v>3.68</v>
+        <v>4.03</v>
       </c>
       <c r="R193" t="n">
-        <v>3.02</v>
+        <v>5.52</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38473,16 +38473,16 @@
         <v>0</v>
       </c>
       <c r="AE193" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF193" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG193" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH193" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI193" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1.71</v>
+        <v>2.43</v>
       </c>
       <c r="Q194" t="n">
-        <v>4.03</v>
+        <v>3.68</v>
       </c>
       <c r="R194" t="n">
-        <v>5.52</v>
+        <v>3.02</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,16 +38670,16 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF194" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG194" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH194" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF195" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -38971,22 +38971,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q197" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39261,10 +39261,10 @@
         <v>0</v>
       </c>
       <c r="AE197" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF197" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>1.37</v>
+        <v>1.92</v>
       </c>
       <c r="Q203" t="n">
-        <v>5.04</v>
+        <v>3.5</v>
       </c>
       <c r="R203" t="n">
-        <v>8.949999999999999</v>
+        <v>4.27</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1.92</v>
+        <v>1.37</v>
       </c>
       <c r="Q205" t="n">
-        <v>3.5</v>
+        <v>5.04</v>
       </c>
       <c r="R205" t="n">
-        <v>4.27</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q214" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q215" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R215" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q217" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q218" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>

--- a/jogos_2026-04-05.xlsx
+++ b/jogos_2026-04-05.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1246,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.03</v>
+        <v>6.17</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.42</v>
+        <v>4.99</v>
       </c>
       <c r="R75" t="n">
-        <v>3.54</v>
+        <v>1.47</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,16 +15227,16 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>4.51</v>
+        <v>1.47</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.96</v>
+        <v>4.99</v>
       </c>
       <c r="R76" t="n">
-        <v>1.69</v>
+        <v>6.17</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,16 +15424,16 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.47</v>
+        <v>4.51</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.99</v>
+        <v>3.96</v>
       </c>
       <c r="R77" t="n">
-        <v>6.17</v>
+        <v>1.69</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,16 +15621,16 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>6.17</v>
+        <v>2.03</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.99</v>
+        <v>3.42</v>
       </c>
       <c r="R78" t="n">
-        <v>1.47</v>
+        <v>3.54</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,16 +15818,16 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>4.57</v>
+        <v>5.96</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.66</v>
+        <v>4.2</v>
       </c>
       <c r="R95" t="n">
-        <v>1.91</v>
+        <v>1.51</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19949,10 +19949,10 @@
         <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20146,10 +20146,10 @@
         <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF132" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF140" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28820,10 +28820,10 @@
         <v>0</v>
       </c>
       <c r="AE144" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF144" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="R147" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29411,10 +29411,10 @@
         <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AF147" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AG147" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="R148" t="n">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AF148" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R149" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AF149" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>6.24</v>
+        <v>0</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30993,10 +30993,10 @@
         <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,10 +31578,10 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF158" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG158" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32175,10 +32175,10 @@
         <v>0</v>
       </c>
       <c r="AG161" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH161" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI161" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF162" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q165" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q174" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q195" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF195" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -38971,22 +38971,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q197" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39365,22 +39365,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="Q198" t="n">
-        <v>3.33</v>
+        <v>2.99</v>
       </c>
       <c r="R198" t="n">
-        <v>3.03</v>
+        <v>2.93</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39458,10 +39458,10 @@
         <v>0</v>
       </c>
       <c r="AE198" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF198" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG198" t="n">
         <v>0</v>
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="Q203" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="R203" t="n">
-        <v>4.27</v>
+        <v>3.06</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40443,10 +40443,10 @@
         <v>0</v>
       </c>
       <c r="AE203" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF203" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG203" t="n">
         <v>0</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>2.42</v>
+        <v>1.92</v>
       </c>
       <c r="Q204" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="R204" t="n">
-        <v>3.06</v>
+        <v>4.27</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40640,10 +40640,10 @@
         <v>0</v>
       </c>
       <c r="AE204" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF204" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG204" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="R211" t="n">
-        <v>2.39</v>
+        <v>3.81</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="R212" t="n">
-        <v>3.81</v>
+        <v>2.39</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q213" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q215" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q217" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="R217" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q218" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>

--- a/jogos_2026-04-05.xlsx
+++ b/jogos_2026-04-05.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.68</v>
+        <v>2.02</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="R46" t="n">
-        <v>2.53</v>
+        <v>3.43</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.47</v>
+        <v>2.03</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.99</v>
+        <v>3.42</v>
       </c>
       <c r="R76" t="n">
-        <v>6.17</v>
+        <v>3.54</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,16 +15424,16 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG76" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.03</v>
+        <v>2.45</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.42</v>
+        <v>3.38</v>
       </c>
       <c r="R78" t="n">
-        <v>3.54</v>
+        <v>2.46</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16021,10 +16021,10 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20146,10 +20146,10 @@
         <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>3.12</v>
+        <v>2.04</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="R101" t="n">
-        <v>2.62</v>
+        <v>4.57</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20343,10 +20343,10 @@
         <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>8.800000000000001</v>
+        <v>2.24</v>
       </c>
       <c r="Q111" t="n">
-        <v>4.3</v>
+        <v>3.24</v>
       </c>
       <c r="R111" t="n">
-        <v>1.37</v>
+        <v>3.24</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF140" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="R148" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF148" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="R149" t="n">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AF149" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,10 +30002,10 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF150" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>6.79</v>
+        <v>2.01</v>
       </c>
       <c r="Q151" t="n">
-        <v>4.85</v>
+        <v>4.06</v>
       </c>
       <c r="R151" t="n">
-        <v>1.4</v>
+        <v>3.68</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,16 +30199,16 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF151" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG151" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH151" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>6.79</v>
       </c>
       <c r="Q152" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30402,10 +30402,10 @@
         <v>0</v>
       </c>
       <c r="AG152" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH152" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI152" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31529,137 +31529,137 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S158" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T158" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U158" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V158" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W158" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X158" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y158" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z158" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA158" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB158" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC158" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD158" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE158" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF158" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG158" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH158" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI158" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ158" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK158" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL158" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM158" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN158" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO158" t="n">
         <v>0</v>
       </c>
       <c r="AP158" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR158" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS158" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT158" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU158" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV158" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW158" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX158" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY158" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ158" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA158" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BB158" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC158" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD158" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE158" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF158" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG158" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31923,137 +31923,137 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P160" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="Q160" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R160" t="n">
-        <v>2.25</v>
+        <v>2.78</v>
       </c>
       <c r="S160" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T160" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U160" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V160" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W160" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X160" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z160" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC160" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD160" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AF160" t="n">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="AG160" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH160" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI160" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ160" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK160" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL160" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM160" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN160" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO160" t="n">
         <v>0</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR160" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS160" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT160" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU160" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV160" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AW160" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX160" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY160" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ160" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BA160" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BB160" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC160" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD160" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE160" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF160" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG160" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>6.24</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32175,10 +32175,10 @@
         <v>0</v>
       </c>
       <c r="AG161" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH161" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI161" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2.84</v>
+        <v>1.43</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="R162" t="n">
-        <v>2.78</v>
+        <v>6.24</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,16 +32366,16 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="n">
         <v>2.15</v>
       </c>
-      <c r="AF162" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG162" t="n">
-        <v>0</v>
-      </c>
       <c r="AH162" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q165" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q170" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q186" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q197" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R197" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>2.42</v>
+        <v>1.37</v>
       </c>
       <c r="Q203" t="n">
-        <v>3.04</v>
+        <v>5.04</v>
       </c>
       <c r="R203" t="n">
-        <v>3.06</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40443,10 +40443,10 @@
         <v>0</v>
       </c>
       <c r="AE203" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF203" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG203" t="n">
         <v>0</v>
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1.37</v>
+        <v>2.42</v>
       </c>
       <c r="Q205" t="n">
-        <v>5.04</v>
+        <v>3.04</v>
       </c>
       <c r="R205" t="n">
-        <v>8.949999999999999</v>
+        <v>3.06</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF205" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q213" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q214" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q217" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q218" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>

--- a/jogos_2026-04-05.xlsx
+++ b/jogos_2026-04-05.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.5</v>
+        <v>3.68</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.86</v>
+        <v>3.22</v>
       </c>
       <c r="R4" t="n">
-        <v>6.1</v>
+        <v>2.06</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1246,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1443,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.16</v>
+        <v>2.02</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="R42" t="n">
-        <v>2.51</v>
+        <v>3.43</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.02</v>
+        <v>2.68</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="R46" t="n">
-        <v>3.43</v>
+        <v>2.53</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.04</v>
+        <v>3.02</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.54</v>
+        <v>3.02</v>
       </c>
       <c r="R52" t="n">
-        <v>3.37</v>
+        <v>2.29</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="R60" t="n">
-        <v>5.16</v>
+        <v>3.37</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>6.17</v>
+        <v>2.03</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.99</v>
+        <v>3.42</v>
       </c>
       <c r="R75" t="n">
-        <v>1.47</v>
+        <v>3.54</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,16 +15227,16 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.03</v>
+        <v>1.47</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.42</v>
+        <v>4.99</v>
       </c>
       <c r="R76" t="n">
-        <v>3.54</v>
+        <v>6.17</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,16 +15424,16 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.45</v>
+        <v>6.17</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.38</v>
+        <v>4.99</v>
       </c>
       <c r="R78" t="n">
-        <v>2.46</v>
+        <v>1.47</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,16 +15818,16 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.47</v>
+        <v>2.45</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.99</v>
+        <v>3.38</v>
       </c>
       <c r="R79" t="n">
-        <v>6.17</v>
+        <v>2.46</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,16 +16015,16 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG79" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.25</v>
+        <v>4.19</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="R96" t="n">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20343,10 +20343,10 @@
         <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21131,10 +21131,10 @@
         <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD105" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.24</v>
+        <v>3.52</v>
       </c>
       <c r="R111" t="n">
-        <v>3.24</v>
+        <v>3.57</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.54</v>
+        <v>3.65</v>
       </c>
       <c r="R124" t="n">
-        <v>3.78</v>
+        <v>5.15</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF130" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF146" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="R147" t="n">
-        <v>3.25</v>
+        <v>5.06</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29411,10 +29411,10 @@
         <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AF147" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AG147" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R148" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AF148" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,10 +30002,10 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF150" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,10 +30199,10 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF151" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG151" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31135,137 +31135,137 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S156" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T156" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U156" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V156" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W156" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X156" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y156" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z156" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC156" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD156" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE156" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF156" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG156" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH156" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI156" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ156" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK156" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL156" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM156" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN156" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO156" t="n">
         <v>0</v>
       </c>
       <c r="AP156" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR156" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS156" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT156" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU156" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV156" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW156" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX156" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY156" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ156" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA156" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BB156" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC156" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD156" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE156" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF156" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31387,10 +31387,10 @@
         <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH157" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31529,137 +31529,137 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P158" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U158" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V158" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W158" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X158" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z158" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF158" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG158" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH158" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI158" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ158" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK158" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL158" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM158" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN158" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO158" t="n">
         <v>0</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR158" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS158" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT158" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU158" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV158" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AW158" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX158" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY158" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ158" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BA158" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BB158" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC158" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD158" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE158" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF158" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG158" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>6.24</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32372,10 +32372,10 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH162" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>1.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="R169" t="n">
-        <v>5.67</v>
+        <v>2.79</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q170" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>2.02</v>
+        <v>1.48</v>
       </c>
       <c r="Q182" t="n">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
       <c r="R182" t="n">
-        <v>3.82</v>
+        <v>6.4</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36306,10 +36306,10 @@
         <v>0</v>
       </c>
       <c r="AE182" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF182" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q185" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38971,22 +38971,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q196" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF196" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39365,22 +39365,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="Q198" t="n">
-        <v>2.99</v>
+        <v>3.33</v>
       </c>
       <c r="R198" t="n">
-        <v>2.93</v>
+        <v>3.03</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39458,10 +39458,10 @@
         <v>0</v>
       </c>
       <c r="AE198" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF198" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG198" t="n">
         <v>0</v>
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="Q204" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="R204" t="n">
-        <v>4.27</v>
+        <v>3.06</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40640,10 +40640,10 @@
         <v>0</v>
       </c>
       <c r="AE204" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF204" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG204" t="n">
         <v>0</v>
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>2.42</v>
+        <v>1.92</v>
       </c>
       <c r="Q205" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="R205" t="n">
-        <v>3.06</v>
+        <v>4.27</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF205" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="R211" t="n">
-        <v>3.81</v>
+        <v>2.39</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="R212" t="n">
-        <v>2.39</v>
+        <v>3.81</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF212" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q214" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q215" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R215" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q217" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="R217" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q218" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>

--- a/jogos_2026-04-05.xlsx
+++ b/jogos_2026-04-05.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.86</v>
+        <v>4.95</v>
       </c>
       <c r="R5" t="n">
-        <v>6.1</v>
+        <v>6.36</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,16 +1437,16 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.95</v>
+        <v>4.86</v>
       </c>
       <c r="R7" t="n">
-        <v>6.36</v>
+        <v>6.1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,16 +1831,16 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.91</v>
+        <v>2.11</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.54</v>
+        <v>3.32</v>
       </c>
       <c r="R11" t="n">
-        <v>1.78</v>
+        <v>3.42</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.68</v>
+        <v>2.02</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="R46" t="n">
-        <v>2.53</v>
+        <v>3.43</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.02</v>
+        <v>1.68</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.02</v>
+        <v>3.52</v>
       </c>
       <c r="R52" t="n">
-        <v>2.29</v>
+        <v>5.16</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.02</v>
+        <v>3.02</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.43</v>
+        <v>3.02</v>
       </c>
       <c r="R59" t="n">
-        <v>3.54</v>
+        <v>2.29</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.03</v>
+        <v>6.17</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.42</v>
+        <v>4.99</v>
       </c>
       <c r="R75" t="n">
-        <v>3.54</v>
+        <v>1.47</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,16 +15227,16 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.47</v>
+        <v>2.03</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.99</v>
+        <v>3.42</v>
       </c>
       <c r="R76" t="n">
-        <v>6.17</v>
+        <v>3.54</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,16 +15424,16 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG76" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>4.51</v>
+        <v>2.45</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.96</v>
+        <v>3.38</v>
       </c>
       <c r="R77" t="n">
-        <v>1.69</v>
+        <v>2.46</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AF77" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>6.17</v>
+        <v>1.47</v>
       </c>
       <c r="Q78" t="n">
         <v>4.99</v>
       </c>
       <c r="R78" t="n">
-        <v>1.47</v>
+        <v>6.17</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15824,10 +15824,10 @@
         <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.45</v>
+        <v>4.51</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.38</v>
+        <v>3.96</v>
       </c>
       <c r="R79" t="n">
-        <v>2.46</v>
+        <v>1.69</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD104" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21131,10 +21131,10 @@
         <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.52</v>
+        <v>3.24</v>
       </c>
       <c r="R111" t="n">
-        <v>3.57</v>
+        <v>3.24</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF140" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q147" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="R147" t="n">
-        <v>5.06</v>
+        <v>3.25</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29411,10 +29411,10 @@
         <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AF147" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="AG147" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="R148" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AF148" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.36</v>
+        <v>1.57</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.41</v>
+        <v>4.3</v>
       </c>
       <c r="R149" t="n">
-        <v>3.35</v>
+        <v>5.06</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AF149" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,10 +30002,10 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF150" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,10 +30199,10 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF151" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG151" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31135,137 +31135,137 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R156" t="n">
-        <v>2.25</v>
+        <v>2.78</v>
       </c>
       <c r="S156" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T156" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U156" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V156" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X156" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z156" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC156" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD156" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AF156" t="n">
-        <v>2.08</v>
+        <v>1.63</v>
       </c>
       <c r="AG156" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH156" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI156" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ156" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK156" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL156" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM156" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN156" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO156" t="n">
         <v>0</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR156" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS156" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT156" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU156" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV156" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AW156" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX156" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY156" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ156" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BA156" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BB156" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC156" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD156" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE156" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF156" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31332,137 +31332,137 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1.43</v>
+        <v>2.85</v>
       </c>
       <c r="Q157" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R157" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S157" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="T157" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U157" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V157" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W157" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X157" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI157" t="n">
         <v>4.8</v>
       </c>
-      <c r="R157" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="S157" t="n">
-        <v>0</v>
-      </c>
-      <c r="T157" t="n">
-        <v>0</v>
-      </c>
-      <c r="U157" t="n">
-        <v>0</v>
-      </c>
-      <c r="V157" t="n">
-        <v>0</v>
-      </c>
-      <c r="W157" t="n">
-        <v>0</v>
-      </c>
-      <c r="X157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG157" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH157" t="n">
+      <c r="AJ157" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ157" t="n">
         <v>1.6</v>
       </c>
-      <c r="AI157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ157" t="n">
-        <v>0</v>
-      </c>
       <c r="AR157" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS157" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU157" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV157" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW157" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX157" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY157" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ157" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA157" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BB157" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC157" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD157" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE157" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF157" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31584,10 +31584,10 @@
         <v>0</v>
       </c>
       <c r="AG158" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH158" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI158" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF160" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q168" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q182" t="n">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="R182" t="n">
-        <v>6.4</v>
+        <v>5.27</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36306,10 +36306,10 @@
         <v>0</v>
       </c>
       <c r="AE182" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF182" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Q184" t="n">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="R184" t="n">
-        <v>5.27</v>
+        <v>6.4</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36700,10 +36700,10 @@
         <v>0</v>
       </c>
       <c r="AE184" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF184" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q185" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q186" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q189" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R189" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -39365,22 +39365,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q198" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>2.42</v>
+        <v>1.92</v>
       </c>
       <c r="Q204" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="R204" t="n">
-        <v>3.06</v>
+        <v>4.27</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40640,10 +40640,10 @@
         <v>0</v>
       </c>
       <c r="AE204" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF204" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG204" t="n">
         <v>0</v>
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="Q205" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="R205" t="n">
-        <v>4.27</v>
+        <v>3.06</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF205" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="R211" t="n">
-        <v>2.39</v>
+        <v>3.81</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="R212" t="n">
-        <v>3.81</v>
+        <v>2.39</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q213" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q215" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>

--- a/jogos_2026-04-05.xlsx
+++ b/jogos_2026-04-05.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.35</v>
+        <v>3.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.95</v>
+        <v>3.22</v>
       </c>
       <c r="R5" t="n">
-        <v>6.36</v>
+        <v>2.06</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.86</v>
+        <v>4.95</v>
       </c>
       <c r="R7" t="n">
-        <v>6.1</v>
+        <v>6.36</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,16 +1831,16 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.68</v>
+        <v>3.16</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="R50" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.38</v>
+        <v>4.99</v>
       </c>
       <c r="R77" t="n">
-        <v>2.46</v>
+        <v>6.17</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,16 +15621,16 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.47</v>
+        <v>4.51</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.99</v>
+        <v>3.96</v>
       </c>
       <c r="R78" t="n">
-        <v>6.17</v>
+        <v>1.69</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,16 +15818,16 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG78" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>4.51</v>
+        <v>2.45</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.96</v>
+        <v>3.38</v>
       </c>
       <c r="R79" t="n">
-        <v>1.69</v>
+        <v>2.46</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AF79" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>4.19</v>
+        <v>2.25</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.7</v>
+        <v>3.36</v>
       </c>
       <c r="R91" t="n">
-        <v>1.97</v>
+        <v>3.1</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21131,10 +21131,10 @@
         <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD105" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>8.800000000000001</v>
+        <v>1.87</v>
       </c>
       <c r="Q114" t="n">
-        <v>4.3</v>
+        <v>3.52</v>
       </c>
       <c r="R114" t="n">
-        <v>1.37</v>
+        <v>3.57</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="R124" t="n">
-        <v>5.15</v>
+        <v>3.78</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.54</v>
+        <v>3.65</v>
       </c>
       <c r="R125" t="n">
-        <v>3.78</v>
+        <v>5.15</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF129" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF130" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF140" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF142" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="R147" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29411,10 +29411,10 @@
         <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AF147" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AG147" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="R148" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AF148" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,10 +30002,10 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF150" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>2.01</v>
+        <v>6.79</v>
       </c>
       <c r="Q151" t="n">
-        <v>4.06</v>
+        <v>4.85</v>
       </c>
       <c r="R151" t="n">
-        <v>3.68</v>
+        <v>1.4</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,16 +30199,16 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF151" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG151" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH151" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>6.79</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30402,10 +30402,10 @@
         <v>0</v>
       </c>
       <c r="AG152" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH152" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI152" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30993,10 +30993,10 @@
         <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH155" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31184,10 +31184,10 @@
         <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF156" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31332,137 +31332,137 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T157" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U157" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V157" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X157" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y157" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z157" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD157" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF157" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH157" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI157" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ157" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK157" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL157" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM157" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN157" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO157" t="n">
         <v>0</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR157" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS157" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT157" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU157" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV157" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AW157" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX157" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY157" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ157" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BA157" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BB157" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC157" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD157" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE157" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF157" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31529,137 +31529,137 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P158" t="n">
-        <v>1.43</v>
+        <v>2.85</v>
       </c>
       <c r="Q158" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R158" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S158" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="T158" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U158" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V158" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W158" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X158" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI158" t="n">
         <v>4.8</v>
       </c>
-      <c r="R158" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="S158" t="n">
-        <v>0</v>
-      </c>
-      <c r="T158" t="n">
-        <v>0</v>
-      </c>
-      <c r="U158" t="n">
-        <v>0</v>
-      </c>
-      <c r="V158" t="n">
-        <v>0</v>
-      </c>
-      <c r="W158" t="n">
-        <v>0</v>
-      </c>
-      <c r="X158" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y158" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG158" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH158" t="n">
+      <c r="AJ158" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ158" t="n">
         <v>1.6</v>
       </c>
-      <c r="AI158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP158" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ158" t="n">
-        <v>0</v>
-      </c>
       <c r="AR158" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS158" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT158" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU158" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV158" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW158" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX158" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY158" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ158" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA158" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BB158" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC158" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD158" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE158" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF158" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG158" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF161" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q165" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q167" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="R167" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>1.56</v>
+        <v>2.18</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.9</v>
+        <v>4.01</v>
       </c>
       <c r="R171" t="n">
-        <v>5.67</v>
+        <v>3.26</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>2.02</v>
+        <v>1.48</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
       <c r="R183" t="n">
-        <v>3.82</v>
+        <v>6.4</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF183" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36700,10 +36700,10 @@
         <v>0</v>
       </c>
       <c r="AE184" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF184" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q185" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q189" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>1.71</v>
+        <v>2.43</v>
       </c>
       <c r="Q193" t="n">
-        <v>4.03</v>
+        <v>3.68</v>
       </c>
       <c r="R193" t="n">
-        <v>5.52</v>
+        <v>3.02</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38473,16 +38473,16 @@
         <v>0</v>
       </c>
       <c r="AE193" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF193" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG193" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH193" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI193" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.68</v>
+        <v>4.03</v>
       </c>
       <c r="R194" t="n">
-        <v>3.02</v>
+        <v>5.52</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,16 +38670,16 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF194" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG194" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH194" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI194" t="n">
         <v>0</v>
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.33</v>
+        <v>2.99</v>
       </c>
       <c r="R195" t="n">
-        <v>3.03</v>
+        <v>2.93</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF195" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q196" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39064,10 +39064,10 @@
         <v>0</v>
       </c>
       <c r="AE196" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF196" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG196" t="n">
         <v>0</v>
@@ -39365,22 +39365,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q198" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>1.37</v>
+        <v>1.92</v>
       </c>
       <c r="Q203" t="n">
-        <v>5.04</v>
+        <v>3.5</v>
       </c>
       <c r="R203" t="n">
-        <v>8.949999999999999</v>
+        <v>4.27</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="Q204" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="R204" t="n">
-        <v>4.27</v>
+        <v>3.06</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40640,10 +40640,10 @@
         <v>0</v>
       </c>
       <c r="AE204" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF204" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG204" t="n">
         <v>0</v>
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>2.42</v>
+        <v>1.37</v>
       </c>
       <c r="Q205" t="n">
-        <v>3.04</v>
+        <v>5.04</v>
       </c>
       <c r="R205" t="n">
-        <v>3.06</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF205" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q213" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q214" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G215" t="n">

--- a/jogos_2026-04-05.xlsx
+++ b/jogos_2026-04-05.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1049,10 +1049,10 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1640,10 +1640,10 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.11</v>
+        <v>3.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="R14" t="n">
-        <v>3.42</v>
+        <v>1.78</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8338,10 +8338,10 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.68</v>
+        <v>2.02</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="R42" t="n">
-        <v>2.53</v>
+        <v>3.43</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.16</v>
+        <v>2.68</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="R50" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.43</v>
+        <v>3.52</v>
       </c>
       <c r="R56" t="n">
-        <v>3.54</v>
+        <v>5.16</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.02</v>
+        <v>3.54</v>
       </c>
       <c r="R63" t="n">
-        <v>2.29</v>
+        <v>3.37</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>6.17</v>
+        <v>2.45</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.99</v>
+        <v>3.38</v>
       </c>
       <c r="R75" t="n">
-        <v>1.47</v>
+        <v>2.46</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,16 +15227,16 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.03</v>
+        <v>1.47</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.42</v>
+        <v>4.99</v>
       </c>
       <c r="R76" t="n">
-        <v>3.54</v>
+        <v>6.17</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,16 +15424,16 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.47</v>
+        <v>6.17</v>
       </c>
       <c r="Q77" t="n">
         <v>4.99</v>
       </c>
       <c r="R77" t="n">
-        <v>6.17</v>
+        <v>1.47</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="R79" t="n">
-        <v>2.46</v>
+        <v>3.54</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.25</v>
+        <v>4.19</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="R91" t="n">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20540,10 +20540,10 @@
         <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21131,10 +21131,10 @@
         <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.69</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.28</v>
+        <v>4.3</v>
       </c>
       <c r="R113" t="n">
-        <v>2.31</v>
+        <v>1.37</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>8.800000000000001</v>
+        <v>2.69</v>
       </c>
       <c r="Q117" t="n">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="R117" t="n">
-        <v>1.37</v>
+        <v>2.31</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="R125" t="n">
-        <v>5.15</v>
+        <v>3.78</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF129" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF137" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28426,10 +28426,10 @@
         <v>0</v>
       </c>
       <c r="AE142" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF142" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="R146" t="n">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AF146" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="R147" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29411,10 +29411,10 @@
         <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF147" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AG147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="R148" t="n">
-        <v>3.25</v>
+        <v>5.06</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AF148" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q149" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="R149" t="n">
-        <v>5.06</v>
+        <v>3.25</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AF149" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>6.79</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30205,10 +30205,10 @@
         <v>0</v>
       </c>
       <c r="AG151" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH151" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>6.79</v>
       </c>
       <c r="Q152" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30402,10 +30402,10 @@
         <v>0</v>
       </c>
       <c r="AG152" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH152" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI152" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>6.24</v>
+        <v>0</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30993,10 +30993,10 @@
         <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31135,137 +31135,137 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S156" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T156" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U156" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V156" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W156" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X156" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y156" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z156" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC156" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD156" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE156" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF156" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG156" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH156" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI156" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ156" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK156" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL156" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM156" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN156" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO156" t="n">
         <v>0</v>
       </c>
       <c r="AP156" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR156" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS156" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT156" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU156" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV156" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW156" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX156" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY156" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ156" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA156" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BB156" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC156" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD156" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE156" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF156" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31529,137 +31529,137 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P158" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T158" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U158" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V158" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W158" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X158" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z158" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA158" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB158" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC158" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD158" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF158" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG158" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH158" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI158" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ158" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK158" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL158" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM158" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN158" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO158" t="n">
         <v>0</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR158" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS158" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT158" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU158" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV158" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AW158" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX158" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY158" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ158" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BA158" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BB158" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC158" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD158" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE158" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF158" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG158" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32372,10 +32372,10 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH162" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="Q182" t="n">
-        <v>4.05</v>
+        <v>3.15</v>
       </c>
       <c r="R182" t="n">
-        <v>5.27</v>
+        <v>3.82</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q183" t="n">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="R183" t="n">
-        <v>6.4</v>
+        <v>5.27</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF183" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>2.02</v>
+        <v>1.48</v>
       </c>
       <c r="Q185" t="n">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
       <c r="R185" t="n">
-        <v>3.82</v>
+        <v>6.4</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -36897,10 +36897,10 @@
         <v>0</v>
       </c>
       <c r="AE185" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF185" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG185" t="n">
         <v>0</v>
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q186" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37395,7 +37395,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="Q193" t="n">
-        <v>3.68</v>
+        <v>4.03</v>
       </c>
       <c r="R193" t="n">
-        <v>3.02</v>
+        <v>5.52</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38473,16 +38473,16 @@
         <v>0</v>
       </c>
       <c r="AE193" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF193" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG193" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH193" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI193" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1.71</v>
+        <v>2.43</v>
       </c>
       <c r="Q194" t="n">
-        <v>4.03</v>
+        <v>3.68</v>
       </c>
       <c r="R194" t="n">
-        <v>5.52</v>
+        <v>3.02</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,16 +38670,16 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF194" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG194" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH194" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI194" t="n">
         <v>0</v>
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>1.92</v>
+        <v>1.37</v>
       </c>
       <c r="Q203" t="n">
-        <v>3.5</v>
+        <v>5.04</v>
       </c>
       <c r="R203" t="n">
-        <v>4.27</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1.37</v>
+        <v>1.92</v>
       </c>
       <c r="Q205" t="n">
-        <v>5.04</v>
+        <v>3.5</v>
       </c>
       <c r="R205" t="n">
-        <v>8.949999999999999</v>
+        <v>4.27</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q213" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q214" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -43546,7 +43546,7 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P219" t="n">

--- a/jogos_2026-04-05.xlsx
+++ b/jogos_2026-04-05.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1640,10 +1640,10 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.95</v>
+        <v>4.86</v>
       </c>
       <c r="R7" t="n">
-        <v>6.36</v>
+        <v>6.1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,16 +1831,16 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8338,10 +8338,10 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.02</v>
+        <v>1.68</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.02</v>
+        <v>3.52</v>
       </c>
       <c r="R59" t="n">
-        <v>2.29</v>
+        <v>5.16</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.02</v>
+        <v>3.02</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.43</v>
+        <v>3.02</v>
       </c>
       <c r="R62" t="n">
-        <v>3.54</v>
+        <v>2.29</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,14 +12818,14 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q63" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="R63" t="n">
         <v>3.54</v>
       </c>
-      <c r="R63" t="n">
-        <v>3.37</v>
-      </c>
       <c r="S63" t="n">
         <v>0</v>
       </c>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.94</v>
+        <v>1.79</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.45</v>
+        <v>4.51</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.38</v>
+        <v>3.96</v>
       </c>
       <c r="R75" t="n">
-        <v>2.46</v>
+        <v>1.69</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.47</v>
+        <v>2.03</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.99</v>
+        <v>3.42</v>
       </c>
       <c r="R76" t="n">
-        <v>6.17</v>
+        <v>3.54</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,16 +15424,16 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG76" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>6.17</v>
+        <v>2.45</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.99</v>
+        <v>3.38</v>
       </c>
       <c r="R77" t="n">
-        <v>1.47</v>
+        <v>2.46</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,16 +15621,16 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG77" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>4.51</v>
+        <v>1.47</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.96</v>
+        <v>4.99</v>
       </c>
       <c r="R78" t="n">
-        <v>1.69</v>
+        <v>6.17</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,16 +15818,16 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.03</v>
+        <v>6.17</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.42</v>
+        <v>4.99</v>
       </c>
       <c r="R79" t="n">
-        <v>3.54</v>
+        <v>1.47</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,16 +16015,16 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>4.19</v>
+        <v>2.25</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.7</v>
+        <v>3.36</v>
       </c>
       <c r="R91" t="n">
-        <v>1.97</v>
+        <v>3.1</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20343,10 +20343,10 @@
         <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20540,10 +20540,10 @@
         <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.87</v>
+        <v>2.69</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.52</v>
+        <v>3.28</v>
       </c>
       <c r="R111" t="n">
-        <v>3.57</v>
+        <v>2.31</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.24</v>
+        <v>3.52</v>
       </c>
       <c r="R112" t="n">
-        <v>3.24</v>
+        <v>3.57</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF132" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF137" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29017,10 +29017,10 @@
         <v>0</v>
       </c>
       <c r="AE145" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF145" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG145" t="n">
         <v>0</v>
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="R146" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AF146" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>1.57</v>
+        <v>2.36</v>
       </c>
       <c r="Q148" t="n">
-        <v>4.3</v>
+        <v>3.41</v>
       </c>
       <c r="R148" t="n">
-        <v>5.06</v>
+        <v>3.35</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AF148" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="R149" t="n">
-        <v>3.25</v>
+        <v>5.06</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AF149" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,10 +30002,10 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF150" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,10 +30199,10 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF151" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG151" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31135,137 +31135,137 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T156" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U156" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V156" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X156" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z156" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC156" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD156" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF156" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG156" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH156" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI156" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ156" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK156" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL156" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM156" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN156" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO156" t="n">
         <v>0</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR156" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS156" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT156" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU156" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV156" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AW156" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX156" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY156" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ156" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BA156" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BB156" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC156" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD156" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE156" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF156" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31387,10 +31387,10 @@
         <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH157" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31923,137 +31923,137 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S160" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T160" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U160" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V160" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W160" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X160" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y160" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z160" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA160" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB160" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC160" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD160" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE160" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF160" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG160" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH160" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI160" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ160" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK160" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL160" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM160" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN160" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO160" t="n">
         <v>0</v>
       </c>
       <c r="AP160" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR160" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS160" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU160" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV160" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW160" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX160" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY160" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ160" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA160" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BB160" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC160" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD160" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE160" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF160" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG160" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32124,13 +32124,13 @@
         </is>
       </c>
       <c r="P161" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
         <v>0</v>
@@ -32169,10 +32169,10 @@
         <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF161" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG161" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>1.43</v>
+        <v>2.84</v>
       </c>
       <c r="Q162" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="R162" t="n">
-        <v>6.24</v>
+        <v>2.78</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,16 +32366,16 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF162" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG162" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH162" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q172" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>2.02</v>
+        <v>1.51</v>
       </c>
       <c r="Q182" t="n">
-        <v>3.15</v>
+        <v>4.05</v>
       </c>
       <c r="R182" t="n">
-        <v>3.82</v>
+        <v>5.27</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q188" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R188" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q189" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R189" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q195" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF195" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -38971,22 +38971,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q196" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q197" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="R197" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39365,22 +39365,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="Q198" t="n">
-        <v>3.33</v>
+        <v>2.99</v>
       </c>
       <c r="R198" t="n">
-        <v>3.03</v>
+        <v>2.93</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39458,10 +39458,10 @@
         <v>0</v>
       </c>
       <c r="AE198" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF198" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG198" t="n">
         <v>0</v>
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>1.37</v>
+        <v>2.42</v>
       </c>
       <c r="Q203" t="n">
-        <v>5.04</v>
+        <v>3.04</v>
       </c>
       <c r="R203" t="n">
-        <v>8.949999999999999</v>
+        <v>3.06</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40443,10 +40443,10 @@
         <v>0</v>
       </c>
       <c r="AE203" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF203" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG203" t="n">
         <v>0</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>2.42</v>
+        <v>1.92</v>
       </c>
       <c r="Q204" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="R204" t="n">
-        <v>3.06</v>
+        <v>4.27</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40640,10 +40640,10 @@
         <v>0</v>
       </c>
       <c r="AE204" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF204" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG204" t="n">
         <v>0</v>
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1.92</v>
+        <v>1.37</v>
       </c>
       <c r="Q205" t="n">
-        <v>3.5</v>
+        <v>5.04</v>
       </c>
       <c r="R205" t="n">
-        <v>4.27</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q207" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF207" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="R211" t="n">
-        <v>3.81</v>
+        <v>2.39</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="R212" t="n">
-        <v>2.39</v>
+        <v>3.81</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF212" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q213" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q215" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R215" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q217" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q218" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>

--- a/jogos_2026-04-05.xlsx
+++ b/jogos_2026-04-05.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1443,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.02</v>
+        <v>2.68</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.54</v>
+        <v>3.38</v>
       </c>
       <c r="R42" t="n">
-        <v>3.43</v>
+        <v>2.53</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.02</v>
+        <v>3.02</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.43</v>
+        <v>3.02</v>
       </c>
       <c r="R63" t="n">
-        <v>3.54</v>
+        <v>2.29</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>4.51</v>
+        <v>1.47</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.96</v>
+        <v>4.99</v>
       </c>
       <c r="R75" t="n">
-        <v>1.69</v>
+        <v>6.17</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,16 +15227,16 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.45</v>
+        <v>6.17</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.38</v>
+        <v>4.99</v>
       </c>
       <c r="R77" t="n">
-        <v>2.46</v>
+        <v>1.47</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,16 +15621,16 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.47</v>
+        <v>4.51</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.99</v>
+        <v>3.96</v>
       </c>
       <c r="R78" t="n">
-        <v>6.17</v>
+        <v>1.69</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,16 +15818,16 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG78" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>6.17</v>
+        <v>2.45</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.99</v>
+        <v>3.38</v>
       </c>
       <c r="R79" t="n">
-        <v>1.47</v>
+        <v>2.46</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,16 +16015,16 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="R127" t="n">
-        <v>5.15</v>
+        <v>3.78</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28623,10 +28623,10 @@
         <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF143" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29017,10 +29017,10 @@
         <v>0</v>
       </c>
       <c r="AE145" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF145" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="R146" t="n">
-        <v>3.25</v>
+        <v>5.06</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AF146" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="R147" t="n">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29411,10 +29411,10 @@
         <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AF147" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AG147" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="R148" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF148" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q149" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="R149" t="n">
-        <v>5.06</v>
+        <v>3.25</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AF149" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>6.79</v>
       </c>
       <c r="Q150" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R150" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30008,10 +30008,10 @@
         <v>0</v>
       </c>
       <c r="AG150" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH150" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,10 +30199,10 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF151" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>6.79</v>
+        <v>2.01</v>
       </c>
       <c r="Q152" t="n">
-        <v>4.85</v>
+        <v>4.06</v>
       </c>
       <c r="R152" t="n">
-        <v>1.4</v>
+        <v>3.68</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,16 +30396,16 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF152" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG152" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH152" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI152" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30987,10 +30987,10 @@
         <v>0</v>
       </c>
       <c r="AE155" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF155" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31135,137 +31135,137 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S156" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T156" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U156" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V156" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W156" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X156" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y156" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z156" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA156" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB156" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC156" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD156" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE156" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF156" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG156" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH156" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI156" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ156" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK156" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL156" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM156" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN156" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO156" t="n">
         <v>0</v>
       </c>
       <c r="AP156" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ156" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR156" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS156" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT156" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU156" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV156" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW156" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX156" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY156" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ156" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA156" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BB156" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC156" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD156" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE156" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF156" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG156" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31923,137 +31923,137 @@
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P160" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T160" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U160" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V160" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W160" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X160" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z160" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA160" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB160" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC160" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD160" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF160" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG160" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH160" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI160" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ160" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK160" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL160" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM160" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN160" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO160" t="n">
         <v>0</v>
       </c>
       <c r="AP160" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR160" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS160" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT160" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU160" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV160" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AW160" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX160" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY160" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ160" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BA160" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BB160" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC160" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD160" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE160" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF160" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG160" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF162" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="Q171" t="n">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="R171" t="n">
-        <v>3.26</v>
+        <v>4.67</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>1.74</v>
+        <v>2.62</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="R172" t="n">
-        <v>4.67</v>
+        <v>2.79</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>1.74</v>
+        <v>2.18</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.53</v>
+        <v>4.01</v>
       </c>
       <c r="R175" t="n">
-        <v>5.4</v>
+        <v>3.26</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>2.3</v>
+        <v>3.67</v>
       </c>
       <c r="Q188" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="R188" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>3.67</v>
+        <v>2.3</v>
       </c>
       <c r="Q189" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="R189" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q196" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="Q197" t="n">
-        <v>3.47</v>
+        <v>2.99</v>
       </c>
       <c r="R197" t="n">
-        <v>4.04</v>
+        <v>2.93</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39261,10 +39261,10 @@
         <v>0</v>
       </c>
       <c r="AE197" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF197" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>2.65</v>
+        <v>1.98</v>
       </c>
       <c r="Q198" t="n">
-        <v>2.99</v>
+        <v>3.47</v>
       </c>
       <c r="R198" t="n">
-        <v>2.93</v>
+        <v>4.04</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39458,10 +39458,10 @@
         <v>0</v>
       </c>
       <c r="AE198" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF198" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG198" t="n">
         <v>0</v>
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>2.42</v>
+        <v>1.92</v>
       </c>
       <c r="Q203" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="R203" t="n">
-        <v>3.06</v>
+        <v>4.27</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40443,10 +40443,10 @@
         <v>0</v>
       </c>
       <c r="AE203" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF203" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG203" t="n">
         <v>0</v>
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>1.92</v>
+        <v>1.37</v>
       </c>
       <c r="Q204" t="n">
-        <v>3.5</v>
+        <v>5.04</v>
       </c>
       <c r="R204" t="n">
-        <v>4.27</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1.37</v>
+        <v>2.42</v>
       </c>
       <c r="Q205" t="n">
-        <v>5.04</v>
+        <v>3.04</v>
       </c>
       <c r="R205" t="n">
-        <v>8.949999999999999</v>
+        <v>3.06</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF205" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q214" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q215" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>

--- a/jogos_2026-04-05.xlsx
+++ b/jogos_2026-04-05.xlsx
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.16</v>
+        <v>2.02</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="R48" t="n">
-        <v>2.51</v>
+        <v>3.43</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.43</v>
+        <v>3.52</v>
       </c>
       <c r="R54" t="n">
-        <v>3.54</v>
+        <v>5.16</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20343,10 +20343,10 @@
         <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20737,10 +20737,10 @@
         <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF132" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF137" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.49</v>
+        <v>3.91</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="R143" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28623,10 +28623,10 @@
         <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF143" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG143" t="n">
         <v>0</v>
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q146" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="R146" t="n">
-        <v>5.06</v>
+        <v>3.25</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AF146" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="R149" t="n">
-        <v>3.25</v>
+        <v>5.06</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AF149" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,10 +30199,10 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF151" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF152" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,13 +30942,13 @@
         </is>
       </c>
       <c r="P155" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S155" t="n">
         <v>0</v>
@@ -30987,10 +30987,10 @@
         <v>0</v>
       </c>
       <c r="AE155" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF155" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31135,137 +31135,137 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T156" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U156" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V156" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W156" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X156" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z156" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA156" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB156" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC156" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD156" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF156" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG156" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH156" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI156" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ156" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK156" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL156" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM156" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN156" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO156" t="n">
         <v>0</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR156" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS156" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT156" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU156" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV156" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AW156" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX156" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY156" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ156" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BA156" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BB156" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC156" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD156" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE156" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF156" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31332,137 +31332,137 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1.43</v>
+        <v>2.85</v>
       </c>
       <c r="Q157" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R157" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S157" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="T157" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U157" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V157" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W157" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X157" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI157" t="n">
         <v>4.8</v>
       </c>
-      <c r="R157" t="n">
-        <v>6.24</v>
-      </c>
-      <c r="S157" t="n">
-        <v>0</v>
-      </c>
-      <c r="T157" t="n">
-        <v>0</v>
-      </c>
-      <c r="U157" t="n">
-        <v>0</v>
-      </c>
-      <c r="V157" t="n">
-        <v>0</v>
-      </c>
-      <c r="W157" t="n">
-        <v>0</v>
-      </c>
-      <c r="X157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y157" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG157" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AH157" t="n">
+      <c r="AJ157" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ157" t="n">
         <v>1.6</v>
       </c>
-      <c r="AI157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ157" t="n">
-        <v>0</v>
-      </c>
       <c r="AR157" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS157" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU157" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV157" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW157" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX157" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY157" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ157" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA157" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BB157" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC157" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD157" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE157" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF157" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31978,10 +31978,10 @@
         <v>0</v>
       </c>
       <c r="AG160" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH160" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI160" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF162" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q168" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R168" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.25</v>
+        <v>4.01</v>
       </c>
       <c r="R172" t="n">
-        <v>2.79</v>
+        <v>3.26</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="Q175" t="n">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="R175" t="n">
-        <v>3.26</v>
+        <v>4.67</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="Q182" t="n">
-        <v>4.05</v>
+        <v>3.15</v>
       </c>
       <c r="R182" t="n">
-        <v>5.27</v>
+        <v>3.82</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF183" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q184" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R184" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q185" t="n">
-        <v>4.25</v>
+        <v>4.05</v>
       </c>
       <c r="R185" t="n">
-        <v>6.4</v>
+        <v>5.27</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -36897,10 +36897,10 @@
         <v>0</v>
       </c>
       <c r="AE185" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF185" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG185" t="n">
         <v>0</v>
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>3.67</v>
+        <v>2.3</v>
       </c>
       <c r="Q188" t="n">
-        <v>2.69</v>
+        <v>2.9</v>
       </c>
       <c r="R188" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37592,22 +37592,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q189" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G202" t="n">

--- a/jogos_2026-04-05.xlsx
+++ b/jogos_2026-04-05.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1443,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1640,10 +1640,10 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.68</v>
+        <v>1.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.22</v>
+        <v>4.95</v>
       </c>
       <c r="R7" t="n">
-        <v>2.06</v>
+        <v>6.36</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.33</v>
+        <v>2.69</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.8</v>
+        <v>3.12</v>
       </c>
       <c r="R69" t="n">
-        <v>8.800000000000001</v>
+        <v>2.65</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.47</v>
+        <v>2.45</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.99</v>
+        <v>3.38</v>
       </c>
       <c r="R75" t="n">
-        <v>6.17</v>
+        <v>2.46</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,16 +15227,16 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG75" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>6.17</v>
+        <v>1.47</v>
       </c>
       <c r="Q77" t="n">
         <v>4.99</v>
       </c>
       <c r="R77" t="n">
-        <v>1.47</v>
+        <v>6.17</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.45</v>
+        <v>6.17</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.38</v>
+        <v>4.99</v>
       </c>
       <c r="R79" t="n">
-        <v>2.46</v>
+        <v>1.47</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,16 +16015,16 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20737,10 +20737,10 @@
         <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD104" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE104" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>8.800000000000001</v>
+        <v>2.24</v>
       </c>
       <c r="Q116" t="n">
-        <v>4.3</v>
+        <v>3.24</v>
       </c>
       <c r="R116" t="n">
-        <v>1.37</v>
+        <v>3.24</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF130" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27441,10 +27441,10 @@
         <v>0</v>
       </c>
       <c r="AE137" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF137" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG137" t="n">
         <v>0</v>
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>1.44</v>
+        <v>3.91</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="R141" t="n">
-        <v>7.85</v>
+        <v>1.75</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>3.91</v>
+        <v>2.49</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="R143" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28623,10 +28623,10 @@
         <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF143" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>2.5</v>
+        <v>1.57</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="R146" t="n">
-        <v>3.25</v>
+        <v>5.06</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AF146" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="R147" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29411,10 +29411,10 @@
         <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF147" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AG147" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R148" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AF148" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.57</v>
+        <v>2.36</v>
       </c>
       <c r="Q149" t="n">
-        <v>4.3</v>
+        <v>3.41</v>
       </c>
       <c r="R149" t="n">
-        <v>5.06</v>
+        <v>3.35</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AF149" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R151" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30199,10 +30199,10 @@
         <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF151" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q152" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF152" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30938,137 +30938,137 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q155" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R155" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S155" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T155" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U155" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V155" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W155" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X155" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y155" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z155" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC155" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD155" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE155" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF155" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG155" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH155" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI155" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ155" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK155" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL155" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM155" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN155" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO155" t="n">
         <v>0</v>
       </c>
       <c r="AP155" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ155" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR155" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS155" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT155" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU155" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV155" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW155" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX155" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY155" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ155" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA155" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BB155" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC155" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD155" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE155" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF155" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31190,10 +31190,10 @@
         <v>0</v>
       </c>
       <c r="AG156" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH156" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31332,137 +31332,137 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T157" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U157" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V157" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X157" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y157" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z157" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD157" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF157" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH157" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI157" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ157" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK157" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL157" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM157" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN157" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO157" t="n">
         <v>0</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR157" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS157" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT157" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU157" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV157" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AW157" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX157" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY157" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ157" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BA157" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BB157" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC157" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD157" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE157" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF157" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>1.43</v>
+        <v>2.84</v>
       </c>
       <c r="Q160" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="R160" t="n">
-        <v>6.24</v>
+        <v>2.78</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,16 +31972,16 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF160" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG160" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH160" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI160" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32366,10 +32366,10 @@
         <v>0</v>
       </c>
       <c r="AE162" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF162" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG162" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q165" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R165" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q167" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R167" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>1.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="R168" t="n">
-        <v>5.67</v>
+        <v>2.79</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R169" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="Q172" t="n">
-        <v>4.01</v>
+        <v>3.53</v>
       </c>
       <c r="R172" t="n">
-        <v>3.26</v>
+        <v>5.4</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>2.02</v>
+        <v>1.51</v>
       </c>
       <c r="Q182" t="n">
-        <v>3.15</v>
+        <v>4.05</v>
       </c>
       <c r="R182" t="n">
-        <v>3.82</v>
+        <v>5.27</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF183" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q184" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36700,10 +36700,10 @@
         <v>0</v>
       </c>
       <c r="AE184" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF184" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="Q185" t="n">
-        <v>4.05</v>
+        <v>3.15</v>
       </c>
       <c r="R185" t="n">
-        <v>5.27</v>
+        <v>3.82</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37395,22 +37395,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37443,13 +37443,13 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q188" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R188" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S188" t="n">
         <v>0</v>
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.43</v>
+        <v>2.65</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.33</v>
+        <v>2.99</v>
       </c>
       <c r="R195" t="n">
-        <v>3.03</v>
+        <v>2.93</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF195" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -38971,22 +38971,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q196" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="Q197" t="n">
-        <v>2.99</v>
+        <v>3.33</v>
       </c>
       <c r="R197" t="n">
-        <v>2.93</v>
+        <v>3.03</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39261,10 +39261,10 @@
         <v>0</v>
       </c>
       <c r="AE197" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF197" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -39365,22 +39365,22 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q198" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="Q203" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="R203" t="n">
-        <v>4.27</v>
+        <v>3.06</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40443,10 +40443,10 @@
         <v>0</v>
       </c>
       <c r="AE203" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF203" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG203" t="n">
         <v>0</v>
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>1.37</v>
+        <v>1.92</v>
       </c>
       <c r="Q204" t="n">
-        <v>5.04</v>
+        <v>3.5</v>
       </c>
       <c r="R204" t="n">
-        <v>8.949999999999999</v>
+        <v>4.27</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40744,7 +40744,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>2.42</v>
+        <v>1.37</v>
       </c>
       <c r="Q205" t="n">
-        <v>3.04</v>
+        <v>5.04</v>
       </c>
       <c r="R205" t="n">
-        <v>3.06</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40837,10 +40837,10 @@
         <v>0</v>
       </c>
       <c r="AE205" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF205" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q206" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R206" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41034,10 +41034,10 @@
         <v>0</v>
       </c>
       <c r="AE206" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF206" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG206" t="n">
         <v>0</v>
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R207" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF207" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="R211" t="n">
-        <v>2.39</v>
+        <v>3.81</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="R212" t="n">
-        <v>3.81</v>
+        <v>2.39</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q217" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="R217" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q218" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>

--- a/jogos_2026-04-05.xlsx
+++ b/jogos_2026-04-05.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>3.68</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.22</v>
+        <v>2.89</v>
       </c>
       <c r="R2" t="n">
-        <v>2.06</v>
+        <v>3.51</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1640,10 +1640,10 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.95</v>
+        <v>4.86</v>
       </c>
       <c r="R7" t="n">
-        <v>6.36</v>
+        <v>6.1</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,16 +1831,16 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.11</v>
+        <v>3.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.32</v>
+        <v>3.54</v>
       </c>
       <c r="R14" t="n">
-        <v>3.42</v>
+        <v>1.78</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.02</v>
+        <v>3.16</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="R46" t="n">
-        <v>3.43</v>
+        <v>2.51</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.47</v>
+        <v>4.51</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.99</v>
+        <v>3.96</v>
       </c>
       <c r="R77" t="n">
-        <v>6.17</v>
+        <v>1.69</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,16 +15621,16 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG77" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>4.51</v>
+        <v>6.17</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.96</v>
+        <v>4.99</v>
       </c>
       <c r="R78" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,16 +15818,16 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>6.17</v>
+        <v>1.47</v>
       </c>
       <c r="Q79" t="n">
         <v>4.99</v>
       </c>
       <c r="R79" t="n">
-        <v>1.47</v>
+        <v>6.17</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16021,10 +16021,10 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.25</v>
+        <v>4.57</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.36</v>
+        <v>3.66</v>
       </c>
       <c r="R96" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.69</v>
+        <v>1.87</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.28</v>
+        <v>3.52</v>
       </c>
       <c r="R111" t="n">
-        <v>2.31</v>
+        <v>3.57</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>8.800000000000001</v>
+        <v>2.69</v>
       </c>
       <c r="Q115" t="n">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="R115" t="n">
-        <v>1.37</v>
+        <v>2.31</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26062,10 +26062,10 @@
         <v>0</v>
       </c>
       <c r="AE130" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF130" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26259,10 +26259,10 @@
         <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF131" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG131" t="n">
         <v>0</v>
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF136" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28623,10 +28623,10 @@
         <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF143" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG143" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1.57</v>
+        <v>2.36</v>
       </c>
       <c r="Q146" t="n">
-        <v>4.3</v>
+        <v>3.41</v>
       </c>
       <c r="R146" t="n">
-        <v>5.06</v>
+        <v>3.35</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="AF146" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.36</v>
+        <v>1.57</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.41</v>
+        <v>4.3</v>
       </c>
       <c r="R149" t="n">
-        <v>3.35</v>
+        <v>5.06</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AF149" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Dundee</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>6.79</v>
+        <v>2.01</v>
       </c>
       <c r="Q150" t="n">
-        <v>4.85</v>
+        <v>4.06</v>
       </c>
       <c r="R150" t="n">
-        <v>1.4</v>
+        <v>3.68</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,16 +30002,16 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF150" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG150" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH150" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI150" t="n">
         <v>0</v>
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Dundee</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>6.79</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30205,10 +30205,10 @@
         <v>0</v>
       </c>
       <c r="AG151" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH151" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q152" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R152" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF152" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30938,137 +30938,137 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P155" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q155" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R155" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S155" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T155" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U155" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V155" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W155" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X155" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y155" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z155" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA155" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB155" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC155" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD155" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE155" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF155" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG155" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH155" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI155" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ155" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK155" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL155" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM155" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN155" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO155" t="n">
         <v>0</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR155" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS155" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT155" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU155" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV155" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AW155" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX155" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY155" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ155" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BA155" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BB155" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC155" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD155" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE155" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF155" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG155" t="n">
         <v>0</v>
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q156" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R156" t="n">
-        <v>6.24</v>
+        <v>0</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31190,10 +31190,10 @@
         <v>0</v>
       </c>
       <c r="AG156" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH156" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31332,137 +31332,137 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S157" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T157" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U157" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V157" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W157" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X157" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y157" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z157" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC157" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD157" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE157" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF157" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG157" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH157" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI157" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ157" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK157" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL157" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM157" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN157" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO157" t="n">
         <v>0</v>
       </c>
       <c r="AP157" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR157" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS157" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU157" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV157" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW157" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX157" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY157" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ157" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA157" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BB157" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC157" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD157" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE157" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF157" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,10 +31578,10 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF158" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG158" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF160" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q162" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R162" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32372,10 +32372,10 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH162" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32915,10 +32915,10 @@
         <v>1.74</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.94</v>
+        <v>3.53</v>
       </c>
       <c r="R165" t="n">
-        <v>4.67</v>
+        <v>5.4</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33503,13 +33503,13 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S168" t="n">
         <v>0</v>
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q170" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q171" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R171" t="n">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q182" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="Q184" t="n">
-        <v>4.25</v>
+        <v>3.15</v>
       </c>
       <c r="R184" t="n">
-        <v>6.4</v>
+        <v>3.82</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36700,10 +36700,10 @@
         <v>0</v>
       </c>
       <c r="AE184" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF184" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>2.02</v>
+        <v>1.48</v>
       </c>
       <c r="Q185" t="n">
-        <v>3.15</v>
+        <v>4.25</v>
       </c>
       <c r="R185" t="n">
-        <v>3.82</v>
+        <v>6.4</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -36897,10 +36897,10 @@
         <v>0</v>
       </c>
       <c r="AE185" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF185" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG185" t="n">
         <v>0</v>
@@ -37198,7 +37198,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -37208,12 +37208,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="Q187" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="R187" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="Q189" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R189" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38971,22 +38971,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q196" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="R196" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="Q197" t="n">
-        <v>3.33</v>
+        <v>3.47</v>
       </c>
       <c r="R197" t="n">
-        <v>3.03</v>
+        <v>4.04</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q198" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q210" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R210" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q213" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q214" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q217" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="R217" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q218" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="R218" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>

--- a/jogos_2026-04-05.xlsx
+++ b/jogos_2026-04-05.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.89</v>
+        <v>3.48</v>
       </c>
       <c r="R2" t="n">
-        <v>3.51</v>
+        <v>3.16</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.68</v>
+        <v>1.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.22</v>
+        <v>4.95</v>
       </c>
       <c r="R3" t="n">
-        <v>2.06</v>
+        <v>6.36</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.02</v>
+        <v>1.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.48</v>
+        <v>4.86</v>
       </c>
       <c r="R4" t="n">
-        <v>3.16</v>
+        <v>6.1</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1246,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.86</v>
+        <v>2.89</v>
       </c>
       <c r="R7" t="n">
-        <v>6.1</v>
+        <v>3.51</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1837,10 +1837,10 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8338,10 +8338,10 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.42</v>
+        <v>3.16</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.75</v>
+        <v>3.34</v>
       </c>
       <c r="R42" t="n">
-        <v>7.5</v>
+        <v>2.51</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="R55" t="n">
-        <v>5.16</v>
+        <v>3.37</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.8</v>
+        <v>3.51</v>
       </c>
       <c r="R74" t="n">
-        <v>8.800000000000001</v>
+        <v>4.75</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="R75" t="n">
-        <v>2.46</v>
+        <v>3.54</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.03</v>
+        <v>4.51</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.42</v>
+        <v>3.96</v>
       </c>
       <c r="R76" t="n">
-        <v>3.54</v>
+        <v>1.69</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>4.51</v>
+        <v>2.45</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.96</v>
+        <v>3.38</v>
       </c>
       <c r="R77" t="n">
-        <v>1.69</v>
+        <v>2.46</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="AF77" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>4.19</v>
+        <v>3.56</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.7</v>
+        <v>3.04</v>
       </c>
       <c r="R84" t="n">
-        <v>1.97</v>
+        <v>2.29</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17788,10 +17788,10 @@
         <v>0</v>
       </c>
       <c r="AE88" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF88" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>5.96</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20540,10 +20540,10 @@
         <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE104" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="R111" t="n">
-        <v>3.57</v>
+        <v>4.04</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>8.800000000000001</v>
+        <v>2.69</v>
       </c>
       <c r="Q112" t="n">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="R112" t="n">
-        <v>1.37</v>
+        <v>2.31</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.07</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="R114" t="n">
-        <v>4.04</v>
+        <v>1.37</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.69</v>
+        <v>2.09</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="R115" t="n">
-        <v>2.31</v>
+        <v>3</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.65</v>
+        <v>3.54</v>
       </c>
       <c r="R124" t="n">
-        <v>5.15</v>
+        <v>3.78</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26259,10 +26259,10 @@
         <v>0</v>
       </c>
       <c r="AE131" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF131" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG131" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF132" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.49</v>
+        <v>3.91</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="R136" t="n">
-        <v>2.75</v>
+        <v>1.75</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27244,10 +27244,10 @@
         <v>0</v>
       </c>
       <c r="AE136" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF136" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF139" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.41</v>
+        <v>3.25</v>
       </c>
       <c r="R146" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AF146" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="R147" t="n">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29411,10 +29411,10 @@
         <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AF147" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AG147" t="n">
         <v>0</v>
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R148" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AF148" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31332,137 +31332,137 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>2.85</v>
+        <v>1.43</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="R157" t="n">
-        <v>2.25</v>
+        <v>6.24</v>
       </c>
       <c r="S157" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T157" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U157" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V157" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X157" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y157" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z157" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA157" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB157" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC157" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD157" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE157" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF157" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AH157" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AI157" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ157" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK157" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL157" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM157" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN157" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO157" t="n">
         <v>0</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR157" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS157" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT157" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU157" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV157" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AW157" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX157" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY157" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ157" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BA157" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BB157" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC157" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD157" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE157" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF157" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,10 +31578,10 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF158" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG158" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF160" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32120,137 +32120,137 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q161" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R161" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S161" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T161" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U161" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V161" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W161" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X161" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y161" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z161" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA161" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB161" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC161" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD161" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE161" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF161" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG161" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH161" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI161" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ161" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK161" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL161" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM161" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN161" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO161" t="n">
         <v>0</v>
       </c>
       <c r="AP161" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR161" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS161" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT161" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU161" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV161" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW161" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX161" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY161" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ161" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA161" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BB161" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC161" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD161" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE161" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF161" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG161" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32321,13 +32321,13 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q162" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R162" t="n">
-        <v>6.24</v>
+        <v>0</v>
       </c>
       <c r="S162" t="n">
         <v>0</v>
@@ -32372,10 +32372,10 @@
         <v>0</v>
       </c>
       <c r="AG162" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH162" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI162" t="n">
         <v>0</v>
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -32912,13 +32912,13 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R165" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33112,10 +33112,10 @@
         <v>1.74</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.94</v>
+        <v>3.53</v>
       </c>
       <c r="R166" t="n">
-        <v>4.67</v>
+        <v>5.4</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="Q167" t="n">
-        <v>4.01</v>
+        <v>3.94</v>
       </c>
       <c r="R167" t="n">
-        <v>3.26</v>
+        <v>4.67</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R170" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q172" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R172" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q173" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R173" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q174" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q182" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R182" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q183" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="R183" t="n">
-        <v>5.27</v>
+        <v>0</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>2.02</v>
+        <v>1.51</v>
       </c>
       <c r="Q184" t="n">
-        <v>3.15</v>
+        <v>4.05</v>
       </c>
       <c r="R184" t="n">
-        <v>3.82</v>
+        <v>5.27</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q186" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R186" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q187" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R187" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>1.71</v>
+        <v>2.43</v>
       </c>
       <c r="Q193" t="n">
-        <v>4.03</v>
+        <v>3.68</v>
       </c>
       <c r="R193" t="n">
-        <v>5.52</v>
+        <v>3.02</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38473,16 +38473,16 @@
         <v>0</v>
       </c>
       <c r="AE193" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF193" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG193" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH193" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI193" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.68</v>
+        <v>4.03</v>
       </c>
       <c r="R194" t="n">
-        <v>3.02</v>
+        <v>5.52</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,16 +38670,16 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF194" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG194" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH194" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI194" t="n">
         <v>0</v>
@@ -38774,7 +38774,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -38784,12 +38784,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>2.65</v>
+        <v>1.98</v>
       </c>
       <c r="Q195" t="n">
-        <v>2.99</v>
+        <v>3.47</v>
       </c>
       <c r="R195" t="n">
-        <v>2.93</v>
+        <v>4.04</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF195" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -38971,7 +38971,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -38981,12 +38981,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q196" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R196" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39168,7 +39168,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>1.98</v>
+        <v>2.65</v>
       </c>
       <c r="Q197" t="n">
-        <v>3.47</v>
+        <v>2.99</v>
       </c>
       <c r="R197" t="n">
-        <v>4.04</v>
+        <v>2.93</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39261,10 +39261,10 @@
         <v>0</v>
       </c>
       <c r="AE197" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF197" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q198" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q206" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R206" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41034,10 +41034,10 @@
         <v>0</v>
       </c>
       <c r="AE206" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF206" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG206" t="n">
         <v>0</v>
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q207" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R207" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF207" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q208" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R208" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41777,13 +41777,13 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q210" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R210" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S210" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q213" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q214" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R214" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G215" t="n">

--- a/jogos_2026-04-05.xlsx
+++ b/jogos_2026-04-05.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.86</v>
+        <v>2.89</v>
       </c>
       <c r="R4" t="n">
-        <v>6.1</v>
+        <v>3.51</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1246,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.68</v>
+        <v>1.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.22</v>
+        <v>4.86</v>
       </c>
       <c r="R6" t="n">
-        <v>2.06</v>
+        <v>6.1</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1640,10 +1640,10 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.11</v>
+        <v>1.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.32</v>
+        <v>4.53</v>
       </c>
       <c r="R12" t="n">
-        <v>3.42</v>
+        <v>4.79</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8338,10 +8338,10 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.02</v>
+        <v>1.42</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.54</v>
+        <v>4.75</v>
       </c>
       <c r="R50" t="n">
-        <v>3.43</v>
+        <v>7.5</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.52</v>
+        <v>3.43</v>
       </c>
       <c r="R54" t="n">
-        <v>5.16</v>
+        <v>3.54</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.51</v>
+        <v>4.8</v>
       </c>
       <c r="R74" t="n">
-        <v>4.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>4.51</v>
+        <v>6.17</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.96</v>
+        <v>4.99</v>
       </c>
       <c r="R76" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,16 +15424,16 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.45</v>
+        <v>4.51</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.38</v>
+        <v>3.96</v>
       </c>
       <c r="R77" t="n">
-        <v>2.46</v>
+        <v>1.69</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>6.17</v>
+        <v>2.45</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.99</v>
+        <v>3.38</v>
       </c>
       <c r="R78" t="n">
-        <v>1.47</v>
+        <v>2.46</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,16 +15818,16 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI78" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>4.19</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>5.96</v>
+        <v>4.19</v>
       </c>
       <c r="Q95" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="R95" t="n">
-        <v>1.51</v>
+        <v>1.97</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AF95" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>5.96</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.36</v>
+        <v>3.64</v>
       </c>
       <c r="R98" t="n">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.04</v>
+        <v>3.12</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="R102" t="n">
-        <v>4.57</v>
+        <v>2.62</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20540,10 +20540,10 @@
         <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>3.12</v>
+        <v>2.04</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="R103" t="n">
-        <v>2.62</v>
+        <v>4.57</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20737,10 +20737,10 @@
         <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="R111" t="n">
-        <v>4.04</v>
+        <v>3.57</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.24</v>
+        <v>4.3</v>
       </c>
       <c r="R113" t="n">
-        <v>3.24</v>
+        <v>1.37</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.52</v>
+        <v>3.24</v>
       </c>
       <c r="R118" t="n">
-        <v>3.57</v>
+        <v>3.24</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.54</v>
+        <v>3.65</v>
       </c>
       <c r="R124" t="n">
-        <v>3.78</v>
+        <v>5.15</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF139" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q142" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29017,10 +29017,10 @@
         <v>0</v>
       </c>
       <c r="AE145" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF145" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG145" t="n">
         <v>0</v>
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="R146" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AF146" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="R148" t="n">
-        <v>2.84</v>
+        <v>5.06</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AF148" t="n">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q149" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="R149" t="n">
-        <v>5.06</v>
+        <v>3.25</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AF149" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -29909,7 +29909,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,10 +30002,10 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AF150" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,13 +30351,13 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q152" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R152" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S152" t="n">
         <v>0</v>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AF152" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31336,13 +31336,13 @@
         </is>
       </c>
       <c r="P157" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R157" t="n">
-        <v>6.24</v>
+        <v>0</v>
       </c>
       <c r="S157" t="n">
         <v>0</v>
@@ -31387,10 +31387,10 @@
         <v>0</v>
       </c>
       <c r="AG157" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH157" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R158" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,10 +31578,10 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF158" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG158" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q159" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R159" t="n">
-        <v>0</v>
+        <v>6.24</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31781,10 +31781,10 @@
         <v>0</v>
       </c>
       <c r="AG159" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH159" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI159" t="n">
         <v>0</v>
@@ -31879,7 +31879,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -31889,12 +31889,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -31927,13 +31927,13 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q160" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S160" t="n">
         <v>0</v>
@@ -31972,10 +31972,10 @@
         <v>0</v>
       </c>
       <c r="AE160" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF160" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AG160" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -32874,12 +32874,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q166" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R166" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>1.74</v>
+        <v>2.62</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="R167" t="n">
-        <v>4.67</v>
+        <v>2.79</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33652,7 +33652,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33700,13 +33700,13 @@
         </is>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R169" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="Q172" t="n">
-        <v>3.25</v>
+        <v>4.01</v>
       </c>
       <c r="R172" t="n">
-        <v>2.79</v>
+        <v>3.26</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34488,13 +34488,13 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R173" t="n">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="S173" t="n">
         <v>0</v>
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>2.18</v>
+        <v>1.56</v>
       </c>
       <c r="Q174" t="n">
-        <v>4.01</v>
+        <v>3.9</v>
       </c>
       <c r="R174" t="n">
-        <v>3.26</v>
+        <v>5.67</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q175" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="R175" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35425,7 +35425,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -35435,12 +35435,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Soroksár SC</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>BVSC</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Soroksár SC</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>BVSC</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q183" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R183" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF183" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q185" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="R185" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -36897,10 +36897,10 @@
         <v>0</v>
       </c>
       <c r="AE185" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF185" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG185" t="n">
         <v>0</v>
@@ -37011,12 +37011,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38193,12 +38193,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -38390,12 +38390,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -38428,13 +38428,13 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>2.43</v>
+        <v>1.71</v>
       </c>
       <c r="Q193" t="n">
-        <v>3.68</v>
+        <v>4.03</v>
       </c>
       <c r="R193" t="n">
-        <v>3.02</v>
+        <v>5.52</v>
       </c>
       <c r="S193" t="n">
         <v>0</v>
@@ -38473,16 +38473,16 @@
         <v>0</v>
       </c>
       <c r="AE193" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF193" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG193" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH193" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AI193" t="n">
         <v>0</v>
@@ -38577,7 +38577,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -38587,12 +38587,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -38625,13 +38625,13 @@
         </is>
       </c>
       <c r="P194" t="n">
-        <v>1.71</v>
+        <v>2.43</v>
       </c>
       <c r="Q194" t="n">
-        <v>4.03</v>
+        <v>3.68</v>
       </c>
       <c r="R194" t="n">
-        <v>5.52</v>
+        <v>3.02</v>
       </c>
       <c r="S194" t="n">
         <v>0</v>
@@ -38670,16 +38670,16 @@
         <v>0</v>
       </c>
       <c r="AE194" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF194" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG194" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH194" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI194" t="n">
         <v>0</v>
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q195" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="R195" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38971,22 +38971,22 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -39019,13 +39019,13 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="Q196" t="n">
-        <v>3.33</v>
+        <v>3.47</v>
       </c>
       <c r="R196" t="n">
-        <v>3.03</v>
+        <v>4.04</v>
       </c>
       <c r="S196" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Q198" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="R198" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>2.42</v>
+        <v>1.37</v>
       </c>
       <c r="Q203" t="n">
-        <v>3.04</v>
+        <v>5.04</v>
       </c>
       <c r="R203" t="n">
-        <v>3.06</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40443,10 +40443,10 @@
         <v>0</v>
       </c>
       <c r="AE203" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF203" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG203" t="n">
         <v>0</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="Q204" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="R204" t="n">
-        <v>4.27</v>
+        <v>3.06</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40640,10 +40640,10 @@
         <v>0</v>
       </c>
       <c r="AE204" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF204" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG204" t="n">
         <v>0</v>
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1.37</v>
+        <v>1.92</v>
       </c>
       <c r="Q205" t="n">
-        <v>5.04</v>
+        <v>3.5</v>
       </c>
       <c r="R205" t="n">
-        <v>8.949999999999999</v>
+        <v>4.27</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -40941,7 +40941,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -40951,12 +40951,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -40989,13 +40989,13 @@
         </is>
       </c>
       <c r="P206" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q206" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R206" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S206" t="n">
         <v>0</v>
@@ -41034,10 +41034,10 @@
         <v>0</v>
       </c>
       <c r="AE206" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF206" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG206" t="n">
         <v>0</v>
@@ -41138,7 +41138,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -41148,12 +41148,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -41186,13 +41186,13 @@
         </is>
       </c>
       <c r="P207" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q207" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R207" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S207" t="n">
         <v>0</v>
@@ -41231,10 +41231,10 @@
         <v>0</v>
       </c>
       <c r="AE207" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF207" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG207" t="n">
         <v>0</v>
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="R211" t="n">
-        <v>3.81</v>
+        <v>2.39</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="R212" t="n">
-        <v>2.39</v>
+        <v>3.81</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF212" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q213" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R213" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42565,13 +42565,13 @@
         </is>
       </c>
       <c r="P214" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q214" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R214" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S214" t="n">
         <v>0</v>
@@ -43108,7 +43108,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -43118,12 +43118,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -43156,13 +43156,13 @@
         </is>
       </c>
       <c r="P217" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q217" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="R217" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="S217" t="n">
         <v>0</v>
@@ -43305,7 +43305,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -43315,12 +43315,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -43353,13 +43353,13 @@
         </is>
       </c>
       <c r="P218" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q218" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="S218" t="n">
         <v>0</v>

--- a/jogos_2026-04-05.xlsx
+++ b/jogos_2026-04-05.xlsx
@@ -753,22 +753,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>SKA Khabarovsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.48</v>
+        <v>2.89</v>
       </c>
       <c r="R2" t="n">
-        <v>3.16</v>
+        <v>3.51</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.35</v>
+        <v>3.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.95</v>
+        <v>3.22</v>
       </c>
       <c r="R3" t="n">
-        <v>6.36</v>
+        <v>2.06</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SKA Khabarovsk</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Melbourne Victory FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.68</v>
+        <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.22</v>
+        <v>4.86</v>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>6.1</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1443,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Melbourne Victory FC</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Wellington Phoenix</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.5</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.86</v>
+        <v>3.48</v>
       </c>
       <c r="R6" t="n">
-        <v>6.1</v>
+        <v>3.16</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1640,10 +1640,10 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.28</v>
+        <v>4.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sporting Delhi</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.02</v>
+        <v>2.02</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.02</v>
+        <v>3.43</v>
       </c>
       <c r="R53" t="n">
-        <v>2.29</v>
+        <v>3.54</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Konyaspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Paderborn</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Nürnberg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nürnberg</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Getafe CF</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Adama Kenema</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima</t>
+          <t>Getafe CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Adama Kenema</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Nakhon Ratchasima</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.33</v>
+        <v>2.69</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.8</v>
+        <v>3.12</v>
       </c>
       <c r="R74" t="n">
-        <v>8.800000000000001</v>
+        <v>2.65</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.03</v>
+        <v>6.17</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.42</v>
+        <v>4.99</v>
       </c>
       <c r="R75" t="n">
-        <v>3.54</v>
+        <v>1.47</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,16 +15227,16 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>6.17</v>
+        <v>2.45</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.99</v>
+        <v>3.38</v>
       </c>
       <c r="R76" t="n">
-        <v>1.47</v>
+        <v>2.46</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,16 +15424,16 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AI76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>4.51</v>
+        <v>1.47</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.96</v>
+        <v>4.99</v>
       </c>
       <c r="R77" t="n">
-        <v>1.69</v>
+        <v>6.17</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,16 +15621,16 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.45</v>
+        <v>2.03</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="R78" t="n">
-        <v>2.46</v>
+        <v>3.54</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.47</v>
+        <v>4.51</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.99</v>
+        <v>3.96</v>
       </c>
       <c r="R79" t="n">
-        <v>6.17</v>
+        <v>1.69</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,16 +16015,16 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG79" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Erokspor</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Norrby</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.25</v>
+        <v>4.57</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.36</v>
+        <v>3.66</v>
       </c>
       <c r="R92" t="n">
-        <v>3.1</v>
+        <v>1.91</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Norrby</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.49</v>
+        <v>3.56</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="R93" t="n">
-        <v>2.67</v>
+        <v>2.29</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Erokspor</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Métlaoui</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Métlaoui</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Dibba Al Fujairah</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Dibba Al Fujairah</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Okzhetpes</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.52</v>
+        <v>3.24</v>
       </c>
       <c r="R111" t="n">
-        <v>3.57</v>
+        <v>3.24</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Mezőkövesd-Zsóry</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>8.800000000000001</v>
+        <v>2.69</v>
       </c>
       <c r="Q113" t="n">
-        <v>4.3</v>
+        <v>3.28</v>
       </c>
       <c r="R113" t="n">
-        <v>1.37</v>
+        <v>2.31</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Karcag SE</t>
+          <t>Strømsgodset</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ajka</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Karcag SE</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Ajka</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Okzhetpes</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Strømsgodset</t>
+          <t>Mezőkövesd-Zsóry</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25865,10 +25865,10 @@
         <v>0</v>
       </c>
       <c r="AE129" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF129" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26456,10 +26456,10 @@
         <v>0</v>
       </c>
       <c r="AE132" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF132" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Rapid Wien</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>3.91</v>
+        <v>2.49</v>
       </c>
       <c r="Q133" t="n">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="R133" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26653,10 +26653,10 @@
         <v>0</v>
       </c>
       <c r="AE133" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF133" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Tiszakécske</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Honvéd W</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Kozármisleny</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Budafoki MTE</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>7.85</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>7.85</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Szentlőrinc SE</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Szeged 2011</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Kozármisleny</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Budafoki MTE</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Tiszakécske</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Honvéd W</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Szeged 2011</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Rapid Wien</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Szentlőrinc SE</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29017,10 +29017,10 @@
         <v>0</v>
       </c>
       <c r="AE145" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF145" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Nantes</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="R146" t="n">
-        <v>2.84</v>
+        <v>5.06</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29214,10 +29214,10 @@
         <v>0</v>
       </c>
       <c r="AE146" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AF146" t="n">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="AG146" t="n">
         <v>0</v>
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Lorient</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Nantes</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="R147" t="n">
-        <v>3.35</v>
+        <v>2.84</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29411,10 +29411,10 @@
         <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AF147" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AG147" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Le Havre</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Auxerre</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q148" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="R148" t="n">
-        <v>5.06</v>
+        <v>3.25</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29608,10 +29608,10 @@
         <v>0</v>
       </c>
       <c r="AE148" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AF148" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="AG148" t="n">
         <v>0</v>
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Le Havre</t>
+          <t>Lorient</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Auxerre</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.25</v>
+        <v>3.41</v>
       </c>
       <c r="R149" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29805,10 +29805,10 @@
         <v>0</v>
       </c>
       <c r="AE149" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AF149" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AG149" t="n">
         <v>0</v>
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -31101,12 +31101,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Pisa</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -31139,13 +31139,13 @@
         </is>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q156" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S156" t="n">
         <v>0</v>
@@ -31184,10 +31184,10 @@
         <v>0</v>
       </c>
       <c r="AE156" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF156" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG156" t="n">
         <v>0</v>
@@ -31288,7 +31288,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -31298,12 +31298,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -31332,137 +31332,137 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S157" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="T157" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U157" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V157" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W157" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X157" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y157" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z157" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC157" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD157" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE157" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF157" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG157" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH157" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI157" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ157" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK157" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL157" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM157" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN157" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO157" t="n">
         <v>0</v>
       </c>
       <c r="AP157" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR157" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS157" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU157" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AV157" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AW157" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX157" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY157" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AZ157" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BA157" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BB157" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC157" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD157" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE157" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF157" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG157" t="n">
         <v>0</v>
@@ -31485,7 +31485,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -31495,12 +31495,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -31533,13 +31533,13 @@
         </is>
       </c>
       <c r="P158" t="n">
-        <v>2.84</v>
+        <v>1.43</v>
       </c>
       <c r="Q158" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="R158" t="n">
-        <v>2.78</v>
+        <v>6.24</v>
       </c>
       <c r="S158" t="n">
         <v>0</v>
@@ -31578,16 +31578,16 @@
         <v>0</v>
       </c>
       <c r="AE158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="n">
         <v>2.15</v>
       </c>
-      <c r="AF158" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AG158" t="n">
-        <v>0</v>
-      </c>
       <c r="AH158" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI158" t="n">
         <v>0</v>
@@ -31682,7 +31682,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -31692,12 +31692,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Silkeborg</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -31730,13 +31730,13 @@
         </is>
       </c>
       <c r="P159" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q159" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R159" t="n">
-        <v>6.24</v>
+        <v>0</v>
       </c>
       <c r="S159" t="n">
         <v>0</v>
@@ -31781,10 +31781,10 @@
         <v>0</v>
       </c>
       <c r="AG159" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH159" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI159" t="n">
         <v>0</v>
@@ -32076,7 +32076,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -32086,12 +32086,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -32120,137 +32120,137 @@
       </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P161" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q161" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R161" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S161" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="T161" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U161" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="V161" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W161" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X161" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z161" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA161" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB161" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC161" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD161" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AE161" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF161" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG161" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AH161" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI161" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ161" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK161" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL161" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM161" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN161" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO161" t="n">
         <v>0</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AR161" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS161" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT161" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU161" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="AV161" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AW161" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX161" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY161" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AZ161" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BA161" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BB161" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC161" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BD161" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE161" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="BF161" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG161" t="n">
         <v>0</v>
@@ -32273,7 +32273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -32283,12 +32283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -33061,7 +33061,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -33071,12 +33071,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>KVC Westerlo</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Sporting Charleroi</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -33109,13 +33109,13 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q166" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R166" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -33258,7 +33258,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -33268,12 +33268,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>KVC Westerlo</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Sporting Charleroi</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>2.62</v>
+        <v>1.56</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="R167" t="n">
-        <v>2.79</v>
+        <v>5.67</v>
       </c>
       <c r="S167" t="n">
         <v>0</v>
@@ -33455,7 +33455,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -33465,12 +33465,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -33662,12 +33662,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -33703,10 +33703,10 @@
         <v>1.74</v>
       </c>
       <c r="Q169" t="n">
-        <v>3.53</v>
+        <v>3.94</v>
       </c>
       <c r="R169" t="n">
-        <v>5.4</v>
+        <v>4.67</v>
       </c>
       <c r="S169" t="n">
         <v>0</v>
@@ -33849,7 +33849,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -33859,12 +33859,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -33897,13 +33897,13 @@
         </is>
       </c>
       <c r="P170" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q170" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="S170" t="n">
         <v>0</v>
@@ -34046,7 +34046,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -34056,12 +34056,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -34094,13 +34094,13 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q171" t="n">
-        <v>0</v>
+        <v>4.01</v>
       </c>
       <c r="R171" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S171" t="n">
         <v>0</v>
@@ -34243,7 +34243,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -34253,12 +34253,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -34291,13 +34291,13 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q172" t="n">
-        <v>4.01</v>
+        <v>0</v>
       </c>
       <c r="R172" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S172" t="n">
         <v>0</v>
@@ -34440,7 +34440,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -34450,12 +34450,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Al Sharjah</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Al Wasl</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -34637,7 +34637,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -34647,12 +34647,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Al Sharjah</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -34685,13 +34685,13 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q174" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R174" t="n">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="S174" t="n">
         <v>0</v>
@@ -34834,7 +34834,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -34844,12 +34844,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -34882,13 +34882,13 @@
         </is>
       </c>
       <c r="P175" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="R175" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="S175" t="n">
         <v>0</v>
@@ -35031,7 +35031,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -35041,12 +35041,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Békéscsaba</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Csákvári TK</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -35228,7 +35228,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -35238,12 +35238,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -35622,7 +35622,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -35632,12 +35632,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Békéscsaba</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Csákvári TK</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -35819,7 +35819,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -35829,12 +35829,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Fenerbahçe</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -36213,7 +36213,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -36223,12 +36223,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -36261,13 +36261,13 @@
         </is>
       </c>
       <c r="P182" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q182" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R182" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="S182" t="n">
         <v>0</v>
@@ -36410,7 +36410,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -36420,12 +36420,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -36458,13 +36458,13 @@
         </is>
       </c>
       <c r="P183" t="n">
-        <v>1.48</v>
+        <v>2.02</v>
       </c>
       <c r="Q183" t="n">
-        <v>4.25</v>
+        <v>3.15</v>
       </c>
       <c r="R183" t="n">
-        <v>6.4</v>
+        <v>3.82</v>
       </c>
       <c r="S183" t="n">
         <v>0</v>
@@ -36503,10 +36503,10 @@
         <v>0</v>
       </c>
       <c r="AE183" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF183" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG183" t="n">
         <v>0</v>
@@ -36607,7 +36607,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -36617,12 +36617,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -36655,13 +36655,13 @@
         </is>
       </c>
       <c r="P184" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Q184" t="n">
-        <v>4.05</v>
+        <v>4.25</v>
       </c>
       <c r="R184" t="n">
-        <v>5.27</v>
+        <v>6.4</v>
       </c>
       <c r="S184" t="n">
         <v>0</v>
@@ -36700,10 +36700,10 @@
         <v>0</v>
       </c>
       <c r="AE184" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF184" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG184" t="n">
         <v>0</v>
@@ -36804,7 +36804,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -36814,12 +36814,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -36852,13 +36852,13 @@
         </is>
       </c>
       <c r="P185" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q185" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="R185" t="n">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="S185" t="n">
         <v>0</v>
@@ -37001,22 +37001,22 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -37049,13 +37049,13 @@
         </is>
       </c>
       <c r="P186" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q186" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R186" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S186" t="n">
         <v>0</v>
@@ -37198,22 +37198,22 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -37246,13 +37246,13 @@
         </is>
       </c>
       <c r="P187" t="n">
-        <v>2.3</v>
+        <v>3.67</v>
       </c>
       <c r="Q187" t="n">
-        <v>2.9</v>
+        <v>2.69</v>
       </c>
       <c r="R187" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="S187" t="n">
         <v>0</v>
@@ -37405,12 +37405,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -37602,12 +37602,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -37640,13 +37640,13 @@
         </is>
       </c>
       <c r="P189" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="Q189" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="R189" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S189" t="n">
         <v>0</v>
@@ -37799,12 +37799,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -37996,12 +37996,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -38774,22 +38774,22 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -38822,13 +38822,13 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q195" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S195" t="n">
         <v>0</v>
@@ -38867,10 +38867,10 @@
         <v>0</v>
       </c>
       <c r="AE195" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF195" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG195" t="n">
         <v>0</v>
@@ -39168,22 +39168,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -39216,13 +39216,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="Q197" t="n">
-        <v>2.99</v>
+        <v>3.33</v>
       </c>
       <c r="R197" t="n">
-        <v>2.93</v>
+        <v>3.03</v>
       </c>
       <c r="S197" t="n">
         <v>0</v>
@@ -39261,10 +39261,10 @@
         <v>0</v>
       </c>
       <c r="AE197" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF197" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG197" t="n">
         <v>0</v>
@@ -39365,7 +39365,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -39375,12 +39375,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -39413,13 +39413,13 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Q198" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S198" t="n">
         <v>0</v>
@@ -39769,12 +39769,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -39966,12 +39966,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -40163,12 +40163,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -40350,7 +40350,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -40360,12 +40360,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>1.37</v>
+        <v>2.42</v>
       </c>
       <c r="Q203" t="n">
-        <v>5.04</v>
+        <v>3.04</v>
       </c>
       <c r="R203" t="n">
-        <v>8.949999999999999</v>
+        <v>3.06</v>
       </c>
       <c r="S203" t="n">
         <v>0</v>
@@ -40443,10 +40443,10 @@
         <v>0</v>
       </c>
       <c r="AE203" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF203" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG203" t="n">
         <v>0</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -40557,12 +40557,12 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -40595,13 +40595,13 @@
         </is>
       </c>
       <c r="P204" t="n">
-        <v>2.42</v>
+        <v>1.92</v>
       </c>
       <c r="Q204" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="R204" t="n">
-        <v>3.06</v>
+        <v>4.27</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -40640,10 +40640,10 @@
         <v>0</v>
       </c>
       <c r="AE204" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AF204" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG204" t="n">
         <v>0</v>
@@ -40754,12 +40754,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -40792,13 +40792,13 @@
         </is>
       </c>
       <c r="P205" t="n">
-        <v>1.92</v>
+        <v>1.37</v>
       </c>
       <c r="Q205" t="n">
-        <v>3.5</v>
+        <v>5.04</v>
       </c>
       <c r="R205" t="n">
-        <v>4.27</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S205" t="n">
         <v>0</v>
@@ -41335,7 +41335,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -41345,12 +41345,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Universidad Chile</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -41383,13 +41383,13 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q208" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R208" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S208" t="n">
         <v>0</v>
@@ -41532,7 +41532,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -41542,12 +41542,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -41580,13 +41580,13 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q209" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="S209" t="n">
         <v>0</v>
@@ -41729,7 +41729,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -41739,12 +41739,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Universidad Chile</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -41936,12 +41936,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -41974,13 +41974,13 @@
         </is>
       </c>
       <c r="P211" t="n">
-        <v>3</v>
+        <v>2.07</v>
       </c>
       <c r="Q211" t="n">
-        <v>3.46</v>
+        <v>3.38</v>
       </c>
       <c r="R211" t="n">
-        <v>2.39</v>
+        <v>3.81</v>
       </c>
       <c r="S211" t="n">
         <v>0</v>
@@ -42019,10 +42019,10 @@
         <v>0</v>
       </c>
       <c r="AE211" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG211" t="n">
         <v>0</v>
@@ -42133,12 +42133,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -42171,13 +42171,13 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="Q212" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="R212" t="n">
-        <v>3.81</v>
+        <v>2.39</v>
       </c>
       <c r="S212" t="n">
         <v>0</v>
@@ -42216,10 +42216,10 @@
         <v>0</v>
       </c>
       <c r="AE212" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG212" t="n">
         <v>0</v>
@@ -42320,7 +42320,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -42330,12 +42330,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -42368,13 +42368,13 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q213" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R213" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="S213" t="n">
         <v>0</v>
@@ -42517,7 +42517,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -42527,12 +42527,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -42714,7 +42714,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -42724,12 +42724,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -42762,13 +42762,13 @@
         </is>
       </c>
       <c r="P215" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q215" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R215" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="S215" t="n">
         <v>0</v>

--- a/jogos_2026-04-05.xlsx
+++ b/jogos_2026-04-05.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Anyang</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>FC Seoul</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Anyang</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>FC Seoul</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.35</v>
+        <v>3.68</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.95</v>
+        <v>3.22</v>
       </c>
       <c r="R7" t="n">
-        <v>6.36</v>
+        <v>2.06</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Sangju Sangmu</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimhae City</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Gimhae City</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.62</v>
+        <v>3.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.53</v>
+        <v>3.54</v>
       </c>
       <c r="R12" t="n">
-        <v>4.79</v>
+        <v>1.78</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sangju Sangmu</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.91</v>
+        <v>1.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.54</v>
+        <v>4.53</v>
       </c>
       <c r="R14" t="n">
-        <v>1.78</v>
+        <v>4.79</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3210,10 +3210,10 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Phu Dong</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.24</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ulytau</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Aktobe</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>3.28</v>
+        <v>4.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="R35" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Phu Dong</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3.16</v>
+        <v>2.68</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.34</v>
+        <v>3.38</v>
       </c>
       <c r="R45" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Zhetysu</t>
+          <t>Ho Chi Minh City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ho Chi Minh City</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Young Lions</t>
+          <t>Sporting Delhi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Balestier Khalsa</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Konyaspor</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Young Lions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Paderborn</t>
+          <t>Balestier Khalsa</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+     